--- a/hardware-carrier/production/BOM.xlsx
+++ b/hardware-carrier/production/BOM.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>22uF 3V3 bulk</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Capacitor 22uF 6.3V X5R 1206</t>
+          <t>Capacitor 1uF 50V X7R 1206</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -585,33 +585,31 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>CL31A226MQHNNNE</t>
+          <t>CL31B105KBHNNNE</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>C159757</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>23.140</t>
-        </is>
+          <t>C1848</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>703670</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.129</v>
+        <v>0.06</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C159757.html</t>
+          <t>https://www.lcsc.com/product-detail/Multilayer-Ceramic-Capacitors-MLCC-SMD-SMT_Samsung-Electro-Mechanics-CL31B105KBHNNNE_C1848.html</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Half the price of the 25 V part (C12891, 0.24 EUR) for the same job. 6.3 V on a 3.3 V rail is roughly a factor of two margin, normal for X5R. Worth knowing: ceramics lose capacitance under DC bias, a 6.3 V part at 3.3 V keeps about half, so 11 to 13 uF rather than 22. Ample for holding up the rail when three transceivers key at once. For the full 22 uF take C12891 (25 V, keeps about 85 %) and pay 12 cents more.</t>
+          <t>The middle rung of the W5500's decoupling. Same Samsung series and package as the 100nF, so one reel family covers both. It closes a factor-220 gap: the rail had 100nF and 22uF and nothing between them.</t>
         </is>
       </c>
     </row>
@@ -622,50 +620,54 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1000uF 35V</t>
+          <t>22uF 3V3 bulk / 22uF W5500</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Electrolytic 1000uF 35V radial, D13 x L20, 5 mm pitch</t>
+          <t>Capacitor 22uF 6.3V X5R 1206</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chengx</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>KM108M035J20RR0VH2FP0</t>
+          <t>CL31A226MQHNNNE</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>C10749</t>
+          <t>C159757</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48.810</t>
+          <t>23.140</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.171</v>
+        <v>0.129</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C10749.html</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>https://www.lcsc.com/product-detail/C159757.html</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Half the price of the 25 V part (C12891, 0.24 EUR) for the same job. 6.3 V on a 3.3 V rail is roughly a factor of two margin, normal for X5R. Worth knowing: ceramics lose capacitance under DC bias, a 6.3 V part at 3.3 V keeps about half, so 11 to 13 uF rather than 22. Ample for holding up the rail when three transceivers key at once. For the full 22 uF take C12891 (25 V, keeps about 85 %) and pay 12 cents more.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -678,46 +680,46 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74AHCT541 pixel buffer</t>
+          <t>1000uF 35V</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Octal buffer 74HCT541, PDIP-20, 300 mil</t>
+          <t>Electrolytic 1000uF 35V radial, D13 x L20, 5 mm pitch</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Chengx</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SN74HCT541N</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>KM108M035J20RR0VH2FP0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>C10749</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>marketplace</t>
+          <t>48.810</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.5</v>
+        <v>0.171</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.5</v>
+        <v>0.17</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://shop.schukat.com/Texas-Instruments/SN74HCT541N/p/37554</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>AHCT or HCT, both have TTL input thresholds (VIH 2.0 V) and therefore switch reliably from the 3.3 V of the ESP32. The only difference is propagation delay, roughly 6 against 14 ns, irrelevant at 1250 ns per WS281x bit. LCSC does not stock the AHCT part in DIP, hence the marketplace sources. Which other types work and which do not is below.</t>
-        </is>
-      </c>
+          <t>https://www.lcsc.com/product-detail/C10749.html</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -730,48 +732,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MF-R 30V</t>
+          <t>74AHCT541 pixel buffer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Polyfuse Bourns MF-R500, 30 V, 5 A hold / 10 A trip, 10.2 mm pitch</t>
+          <t>Octal buffer 74HCT541, PDIP-20, 300 mil</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>MF-R500</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>C208489</t>
-        </is>
-      </c>
+          <t>SN74HCT541N</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>marketplace</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.419</v>
+        <v>1.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C208489.html</t>
+          <t>https://shop.schukat.com/Texas-Instruments/SN74HCT541N/p/37554</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>The largest that fits the current placement: body 17.4 x 3.0 mm, 3.8 mm clear of the 1000uF can. Sits in the left and right hole (10.2 mm pitch). The MF-R900 (9 A, C208493) is the largest of the series but its body is 24.2 mm and would come within 0.40 mm of the can; both parts stand 20 to 25 mm tall. MF-RHT and MF-RG are 16 V parts above 1 A and unusable on 24 V.</t>
+          <t>AHCT or HCT, both have TTL input thresholds (VIH 2.0 V) and therefore switch reliably from the 3.3 V of the ESP32. The only difference is propagation delay, roughly 6 against 14 ns, irrelevant at 1250 ns per WS281x bit. LCSC does not stock the AHCT part in DIP, hence the marketplace sources. Which other types work and which do not is below.</t>
         </is>
       </c>
     </row>
@@ -782,50 +780,54 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10k ETH_CS pu / 10k ETH_RST pu / 10k dir</t>
+          <t>MF-R 30V</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Resistor 10k 1206 1%</t>
+          <t>Polyfuse Bourns MF-R500, 30 V, 5 A hold / 10 A trip, 10.2 mm pitch</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1206W4F1002T5E</t>
+          <t>MF-R500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>C17902</t>
+          <t>C208489</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>204.500</t>
+          <t>644</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.018</v>
+        <v>0.419</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C17902.html</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>https://www.lcsc.com/product-detail/C208489.html</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>The largest that fits the current placement: body 17.4 x 3.0 mm, 3.8 mm clear of the 1000uF can. Sits in the left and right hole (10.2 mm pitch). The MF-R900 (9 A, C208493) is the largest of the series but its body is 24.2 mm and would come within 0.40 mm of the can; both parts stand 20 to 25 mm tall. MF-RHT and MF-RG are 16 V parts above 1 A and unusable on 24 V.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -834,16 +836,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>120R term</t>
+          <t>10k ETH_CS pu / 10k ETH_RST pu / 10k dir</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Resistor 120R 1206 1%</t>
+          <t>Resistor 10k 1206 1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -853,27 +855,31 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1206W4F1200T5E</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>1206W4F1002T5E</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>C17902</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>204.500</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Same series as the verified 10k. The C number could not be confirmed by search, look up the manufacturer part number on LCSC.</t>
-        </is>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lcsc.com/product-detail/C17902.html</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -882,16 +888,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>330R bias+ / 330R bias-</t>
+          <t>120R term</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Resistor 330R 1206 5% (fail-safe bias)</t>
+          <t>Resistor 120R 1206 1%</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -901,33 +907,25 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1206W4J0331T5E</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>C25374</t>
-        </is>
-      </c>
+          <t>1206W4F1200T5E</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79.100</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lcsc.com/product-detail/Chip-Resistor-Surface-Mount_Uniroyal-Elec-1206W4J0331T5E_C25374.html</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Fail-safe bias on a 3.3 V bus needs more than 200 mV idle differential. With two terminators (60 R, the normal case once this board is the controller at one end) 330 R gives 275 mV, 470 R only 198 mV. Anything from 270 R to 430 R works, see the table. Bus loading 4.6 mA, which no RS-485 driver cares about, and 5 % tolerance is irrelevant for a bias resistor. The land takes anything from 0402 to 1206: copper runs 0.30 to 2.30 mm off centre, so every end cap lands on it, an 0402's at 0.25 to 0.50 as much as a 1206's at 1.10 to 1.60. The 390R that only exists in 0805 therefore goes in without any trickery.</t>
+          <t>Same series as the verified 10k. The C number could not be confirmed by search, look up the manufacturer part number on LCSC.</t>
         </is>
       </c>
     </row>
@@ -938,50 +936,54 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12-24V IN 24A</t>
+          <t>330R bias+ / 330R bias- / 330R pixel</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Screw terminal, 2 pole, 5.08 mm pitch, 24 A</t>
+          <t>Resistor 330R 1206 5% (fail-safe bias)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Cixi Kefa</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>KF128-5.08-2P-AA</t>
+          <t>1206W4J0331T5E</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>C474952</t>
+          <t>C25374</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63.515</t>
+          <t>79.100</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.177</v>
+        <v>0.012</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>https://www.lcsc.com/product-detail/C474952.html</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>https://www.lcsc.com/product-detail/Chip-Resistor-Surface-Mount_Uniroyal-Elec-1206W4J0331T5E_C25374.html</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Fail-safe bias on a 3.3 V bus needs more than 200 mV idle differential. With two terminators (60 R, the normal case once this board is the controller at one end) 330 R gives 275 mV, 470 R only 198 mV. Anything from 270 R to 430 R works, see the table. Bus loading 4.6 mA, which no RS-485 driver cares about, and 5 % tolerance is irrelevant for a bias resistor. The land takes anything from 0402 to 1206: copper runs 0.30 to 2.30 mm off centre, so every end cap lands on it, an 0402's at 0.25 to 0.50 as much as a 1206's at 1.10 to 1.60. The 390R that only exists in 0805 therefore goes in without any trickery.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -990,16 +992,16 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PIXn V+/DATA/GND</t>
+          <t>12-24V IN 24A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Screw terminal, 3 pole, 5.08 mm pitch</t>
+          <t>Screw terminal, 2 pole, 5.08 mm pitch, 24 A</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1009,28 +1011,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>KF128-5.08-3P-AA</t>
+          <t>KF128-5.08-2P-AA</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>C474953</t>
+          <t>C474952</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16.545</t>
+          <t>63.515</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.88</v>
+        <v>0.18</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>https://lcsc.com/product-detail/Screw-terminal_Cixi-Kefa-Elec-KF128-5-08-3P-AA_C474953.html</t>
+          <t>https://www.lcsc.com/product-detail/C474952.html</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1042,50 +1044,102 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PIXn V+/DATA/GND</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Screw terminal, 3 pole, 5.08 mm pitch</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cixi Kefa</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>KF128-5.08-3P-AA</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>C474953</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16.545</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://lcsc.com/product-detail/Screw-terminal_Cixi-Kefa-Elec-KF128-5-08-3P-AA_C474953.html</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>TVS bidir</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>TVS bidirectional SMF12CA, SOD-123FL, 12 V standoff, 200 W</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Jingdao Microelectronics</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SMF12CA</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>C353317</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>184.100</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>0.022</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>https://lcsc.com/product-detail/TVS_Shandong-Jingdao-Microelectronics-SMF12CA_C353317.html</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>The land is universal: copper runs from 0.30 to 2.90 mm off centre, so SOD-123, SOD-123F, SOD-123FL, DO-214AC (SMA) and a plain 1206 all sit on it. SMF12CA in SOD-123FL is the cheap default. SMAJ12CA in SMA is the same diode at 400 W instead of 200 W, same 12 V standoff and the same breakdown window, and its feet reach 2.80 mm so it now lands properly rather than hanging off the end. VRWM 12 V, so it does not conduct at the +12 V common mode RS-485 allows, VBR 14.7 V, clamps at 19.9 V with 10 A. Two per port, A and B to GND. A varistor is no substitute, it would not clamp until about 40 V.</t>
         </is>
@@ -1107,7 +1161,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -1302,11 +1356,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>330R bias+ / 330R bias-</t>
+          <t>330R bias+ / 330R bias- / 330R pixel</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
